--- a/data/中幼林抚育-网格填表模板2.xlsx
+++ b/data/中幼林抚育-网格填表模板2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26540" windowHeight="14260"/>
+    <workbookView windowWidth="26540" windowHeight="14260" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15305" uniqueCount="1444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15307" uniqueCount="1446">
   <si>
     <t>项目名称</t>
   </si>
@@ -4363,6 +4363,12 @@
   </si>
   <si>
     <t>unique-key</t>
+  </si>
+  <si>
+    <t>导出筛选</t>
+  </si>
+  <si>
+    <t>验收人|select;验收日期|date;验收结果|select;标段|select;乡镇|select</t>
   </si>
 </sst>
 </file>
@@ -57162,7 +57168,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="22.2692307692308" customWidth="1"/>
@@ -57395,6 +57401,14 @@
         <v>5</v>
       </c>
     </row>
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
+        <v>1444</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1445</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
